--- a/docentes/Castillo Cruz Carlos Samuel - Estadisticos 20232.xlsx
+++ b/docentes/Castillo Cruz Carlos Samuel - Estadisticos 20232.xlsx
@@ -530,16 +530,19 @@
         <v>14</v>
       </c>
       <c r="D2">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>85.70999999999999</v>
+      </c>
+      <c r="H2">
+        <v>8.6</v>
       </c>
     </row>
   </sheetData>
@@ -595,16 +598,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G2">
-        <v>71.43000000000001</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Castillo Cruz Carlos Samuel - Estadisticos 20232.xlsx
+++ b/docentes/Castillo Cruz Carlos Samuel - Estadisticos 20232.xlsx
@@ -462,7 +462,7 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -471,13 +471,13 @@
         <v>4</v>
       </c>
       <c r="F2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="H2">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -527,7 +527,7 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -536,13 +536,13 @@
         <v>2</v>
       </c>
       <c r="F2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="H2">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -592,22 +592,22 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G2">
-        <v>85.70999999999999</v>
+        <v>93.33</v>
       </c>
       <c r="H2">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
     </row>
   </sheetData>
